--- a/7bus_ems_input_data.xlsx
+++ b/7bus_ems_input_data.xlsx
@@ -171,7 +171,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -185,11 +185,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -282,6 +310,8 @@
     <xf numFmtId="0" fontId="4" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -667,6 +697,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -731,7 +762,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>1.05</v>
@@ -763,7 +794,7 @@
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>1.05</v>
@@ -795,7 +826,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
@@ -829,7 +860,7 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>22.9</v>
+        <v>154</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
@@ -863,7 +894,7 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>22.9</v>
+        <v>154</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
@@ -897,7 +928,7 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>22.9</v>
+        <v>154</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -931,7 +962,7 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>22.9</v>
+        <v>154</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
@@ -945,6 +976,7 @@
         <v>450</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -996,6 +1028,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1258,6 +1291,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -1297,12 +1331,17 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>① 부하 설정 (loads)</t>
         </is>
       </c>
+      <c r="B3" s="32" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="33" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -1425,12 +1464,17 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>② 발전기 설정</t>
         </is>
       </c>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="33" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -1540,12 +1584,17 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
           <t>③ 차단기 상태 (breakers)</t>
         </is>
       </c>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="33" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
@@ -1760,12 +1809,19 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>① 모선 해석 결과</t>
         </is>
       </c>
+      <c r="B3" s="32" t="n"/>
+      <c r="C3" s="32" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
+      <c r="F3" s="32" t="n"/>
+      <c r="G3" s="33" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
@@ -2049,12 +2105,19 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>② NR 수렴 추이</t>
         </is>
       </c>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="33" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
@@ -2238,12 +2301,19 @@
       <c r="F19" s="24" t="inlineStr"/>
       <c r="G19" s="24" t="inlineStr"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>③ 전체 집계</t>
         </is>
       </c>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="33" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="28" t="inlineStr">

--- a/7bus_ems_input_data.xlsx
+++ b/7bus_ems_input_data.xlsx
@@ -697,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -976,7 +975,6 @@
         <v>450</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -1028,7 +1026,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1097,18 +1094,18 @@
         <v>6</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.01</v>
+        <v>0.0015</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>10.0000−j30.0000</t>
+          <t>6.60-j66.01</t>
         </is>
       </c>
       <c r="H4" s="9" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -1132,18 +1129,18 @@
         <v>6</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.01</v>
+        <v>0.0015</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>10.0000−j30.0000</t>
+          <t>6.60-j66.01</t>
         </is>
       </c>
       <c r="H5" s="9" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -1167,18 +1164,18 @@
         <v>7</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.02</v>
+        <v>0.001</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>1.9231−j9.6154</t>
+          <t>0.62-j24.98</t>
         </is>
       </c>
       <c r="H6" s="12" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
@@ -1202,18 +1199,18 @@
         <v>3</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>1.6598−j6.2241</t>
+          <t>1.92-j9.62</t>
         </is>
       </c>
       <c r="H7" s="9" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -1237,18 +1234,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>1.6598−j6.2241</t>
+          <t>1.92-j9.62</t>
         </is>
       </c>
       <c r="H8" s="9" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -1272,18 +1269,18 @@
         <v>5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>1.6598−j6.2241</t>
+          <t>1.92-j9.62</t>
         </is>
       </c>
       <c r="H9" s="9" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -1291,7 +1288,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -1331,7 +1327,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1464,7 +1459,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -1584,7 +1578,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -1809,7 +1802,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1863,7 @@
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>1.050</t>
+          <t>1.0500</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -1881,7 +1873,7 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="F5" s="23" t="inlineStr">
@@ -1906,12 +1898,12 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>1.050</t>
+          <t>1.0500</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>+0.108</t>
+          <t>+0.073</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -1941,12 +1933,12 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>1.0468</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>−0.564</t>
+          <t>−0.304</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -1976,12 +1968,12 @@
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>1.0327</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>−5.313</t>
+          <t>−2.208</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -1996,7 +1988,7 @@
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>정상 (배전)</t>
+          <t>정상 (변전)</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2003,12 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>1.0167</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>−7.830</t>
+          <t>−3.737</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -2046,12 +2038,12 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>1.0195</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>−7.399</t>
+          <t>−3.479</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -2081,12 +2073,12 @@
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>1.0139</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>−8.266</t>
+          <t>−3.997</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -2101,11 +2093,10 @@
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>⚠ 최저전압</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -2164,12 +2155,12 @@
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>3.000e+0</t>
+          <t>6.601e+0</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>300 MW</t>
+          <t>660 MW</t>
         </is>
       </c>
       <c r="D15" s="26" t="inlineStr">
@@ -2193,12 +2184,12 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>1.759e−1</t>
+          <t>3.629e−1</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 17.6 MW</t>
+          <t>36.3 MW</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
@@ -2222,17 +2213,17 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>1.517e−3</t>
+          <t>1.071e−3</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.15 MW</t>
+          <t>0.11 MW</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>ΔP @ Bus7</t>
+          <t>ΔQ @ Bus6</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -2251,17 +2242,17 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>8.614e−7</t>
+          <t>1.351e−8</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>0.00009 MW</t>
+          <t>~0</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>ΔP @ Bus7</t>
+          <t>ΔQ @ Bus6</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -2280,7 +2271,7 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2.020e−13</t>
+          <t>4.834e−14</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -2290,7 +2281,7 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>ΔP @ Bus7</t>
+          <t>ΔQ @ Bus6</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -2301,7 +2292,6 @@
       <c r="F19" s="24" t="inlineStr"/>
       <c r="G19" s="24" t="inlineStr"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
@@ -2323,7 +2313,7 @@
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>93.83 MW</t>
+          <t>90.74 MW</t>
         </is>
       </c>
       <c r="C22" s="30" t="inlineStr"/>
@@ -2348,7 +2338,7 @@
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
-          <t>3.83 MW</t>
+          <t>0.74 MW (0.82%)</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr"/>
@@ -2359,7 +2349,7 @@
       </c>
       <c r="E23" s="30" t="inlineStr">
         <is>
-          <t>4회</t>
+          <t>5회</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr"/>
@@ -2373,7 +2363,7 @@
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>Bus5 = 0.947 pu</t>
+          <t>Bus5 = 1.014 pu</t>
         </is>
       </c>
       <c r="C24" s="30" t="inlineStr"/>
